--- a/travel/2026-11_JFM-GRIPS_survey/学会出席等出張許可申請書_11月15-17日_大分調査.xlsx
+++ b/travel/2026-11_JFM-GRIPS_survey/学会出席等出張許可申請書_11月15-17日_大分調査.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>学会出席等出張許可申請書</t>
     <rPh sb="0" eb="2">
@@ -633,10 +633,7 @@
   </si>
   <si>
     <t xml:space="preserve">（大学の行事等と重なった日に出張を予定する場合は、その理由を記入ください）
-16日（月）9時30分から大分県庁で調査を行うため、調査研究会の行程に従い前日15日（日）に大分市へ移動して前泊する。調査日程は調査先の県・市と調整して決めたもので、変更できない。16日（月）3限「EU経済論Ⅱ」・4限「ゼミ」と重なるため、休講とし補講で対応する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">支障なし・休講（○：11/16 月3限・4限）・代講（　　　　　　）</t>
+16日（月）9時30分から大分県庁で調査を行うため、調査研究会の行程に従い前日15日（日）に大分市へ移動して前泊する。調査日程は調査先の県・市と調整して決めたもので、変更できない。16日（月）3限「EU経済論Ⅱ」・4限「ゼミ」は、オンデマンド教材の配信で授業を行うため、授業への支障はない。</t>
   </si>
 </sst>
 </file>
@@ -1201,6 +1198,72 @@
           </a:ext>
         </a:extLst>
       </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="楕円 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0268137-793E-52F9-1BEF-740E3DD6C2FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1752600" y="6143625"/>
+          <a:ext cx="647700" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1805,7 +1868,7 @@
         <v>3</v>
       </c>
       <c r="Y2" s="8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z2" s="7" t="s">
         <v>4</v>
@@ -2290,7 +2353,7 @@
       </c>
       <c r="F16" s="46"/>
       <c r="G16" s="62" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H16" s="62"/>
       <c r="I16" s="62"/>
